--- a/“YUDX”BOM.xlsx
+++ b/“YUDX”BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\“聿”DOC\英文要发布的资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GitHub\YUDX-tool-changer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB0288B-999F-409B-AE32-EE90BB533148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D9D41F-559D-4EAA-AD37-BC4886064FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -397,7 +397,7 @@
   <si>
     <t>Info: 1. The finished YUDX extruder kit may be released in the coming months. You may wait for its launch.
 2. Amazon links were found by Claude Code. Links may be incorrect, please feedback any errors to me.
-3. discord:https://discord.gg/vE4ExaVR3
+3. discord:https://discord.gg/huHw8kzNXp
 4. https://github.com/dumplinglab/YUDX-tool-changer</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
